--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-lm-seltene.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-lm-seltene.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T09:29:03+00:00</t>
+    <t>2026-09-02T14:14:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -314,7 +314,7 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>Seltene.AnamneseUndDiagnostik</t>
+    <t>Seltene.anamneseUndDiagnostik</t>
   </si>
   <si>
     <t xml:space="preserve">BackboneElement
@@ -324,13 +324,13 @@
     <t>Diagnose</t>
   </si>
   <si>
-    <t>Seltene.AnamneseUndDiagnostik.id</t>
-  </si>
-  <si>
-    <t>Seltene.AnamneseUndDiagnostik.extension</t>
-  </si>
-  <si>
-    <t>Seltene.AnamneseUndDiagnostik.modifierExtension</t>
+    <t>Seltene.anamneseUndDiagnostik.id</t>
+  </si>
+  <si>
+    <t>Seltene.anamneseUndDiagnostik.extension</t>
+  </si>
+  <si>
+    <t>Seltene.anamneseUndDiagnostik.modifierExtension</t>
   </si>
   <si>
     <t>extensions
@@ -353,7 +353,7 @@
     <t>BackboneElement.modifierExtension</t>
   </si>
   <si>
-    <t>Seltene.AnamneseUndDiagnostik.Untersuchungsdatum</t>
+    <t>Seltene.anamneseUndDiagnostik.untersuchungsdatum</t>
   </si>
   <si>
     <t xml:space="preserve">date
@@ -366,7 +366,7 @@
     <t>Datum der durchgeführten Untersuchung eines SE-Patienten.</t>
   </si>
   <si>
-    <t>Seltene.AnamneseUndDiagnostik.Untersuchungsanlass</t>
+    <t>Seltene.anamneseUndDiagnostik.untersuchungsanlass</t>
   </si>
   <si>
     <t xml:space="preserve">code
@@ -379,22 +379,22 @@
     <t>Grund fuer den Besuch des SE-Patienten.</t>
   </si>
   <si>
-    <t>Seltene.AnamneseUndDiagnostik.Phaenotypisierung</t>
+    <t>Seltene.anamneseUndDiagnostik.phaenotypisierung</t>
   </si>
   <si>
     <t>Phaenotypisierung</t>
   </si>
   <si>
-    <t>Seltene.AnamneseUndDiagnostik.Phaenotypisierung.id</t>
-  </si>
-  <si>
-    <t>Seltene.AnamneseUndDiagnostik.Phaenotypisierung.extension</t>
-  </si>
-  <si>
-    <t>Seltene.AnamneseUndDiagnostik.Phaenotypisierung.modifierExtension</t>
-  </si>
-  <si>
-    <t>Seltene.AnamneseUndDiagnostik.Phaenotypisierung.HPOTerm</t>
+    <t>Seltene.anamneseUndDiagnostik.phaenotypisierung.id</t>
+  </si>
+  <si>
+    <t>Seltene.anamneseUndDiagnostik.phaenotypisierung.extension</t>
+  </si>
+  <si>
+    <t>Seltene.anamneseUndDiagnostik.phaenotypisierung.modifierExtension</t>
+  </si>
+  <si>
+    <t>Seltene.anamneseUndDiagnostik.phaenotypisierung.hpoTerm</t>
   </si>
   <si>
     <t>HPO-Term des Symptoms</t>
@@ -403,7 +403,7 @@
     <t>Phaenotypisierung des SE-Patienten mittels HPO-Term (Human Phenotype Ontology) oder anderer Terminologien (SNOMED CT, ICD-10, LOINC).</t>
   </si>
   <si>
-    <t>Seltene.AnamneseUndDiagnostik.Phaenotypisierung.HPOExcluded</t>
+    <t>Seltene.anamneseUndDiagnostik.phaenotypisierung.hpoExcluded</t>
   </si>
   <si>
     <t xml:space="preserve">boolean
@@ -416,7 +416,7 @@
     <t>Gibt an, ob das HPO-Merkmal explizit ausgeschlossen wurde (negated finding). Abgeleitet aus valueCodeableConcept: LOINC LA9634-2 'Absent' = true, LA9633-4 'Present' = false. Folgt HL7 Phenomics IG Muster.</t>
   </si>
   <si>
-    <t>Seltene.AnamneseUndDiagnostik.Phaenotypisierung.HPOStatus</t>
+    <t>Seltene.anamneseUndDiagnostik.phaenotypisierung.hpoStatus</t>
   </si>
   <si>
     <t>Status HPO-Term</t>
@@ -425,7 +425,7 @@
     <t>Status oder Schweregrad des Phaenotyps (Present/Absent/Severity).</t>
   </si>
   <si>
-    <t>Seltene.AnamneseUndDiagnostik.Phaenotypisierung.HPOVersion</t>
+    <t>Seltene.anamneseUndDiagnostik.phaenotypisierung.hpoVersion</t>
   </si>
   <si>
     <t>Version HPO-Term</t>
@@ -434,22 +434,22 @@
     <t>Kennzeichnung der genutzten Version des ausgewaehlten HPO-Terms.</t>
   </si>
   <si>
-    <t>Seltene.AnamneseUndDiagnostik.Phaenotypisierung.ZeitraumSymptom</t>
+    <t>Seltene.anamneseUndDiagnostik.phaenotypisierung.zeitraumSymptom</t>
   </si>
   <si>
     <t>Zeitraum des Symptom</t>
   </si>
   <si>
-    <t>Seltene.AnamneseUndDiagnostik.Phaenotypisierung.ZeitraumSymptom.id</t>
-  </si>
-  <si>
-    <t>Seltene.AnamneseUndDiagnostik.Phaenotypisierung.ZeitraumSymptom.extension</t>
-  </si>
-  <si>
-    <t>Seltene.AnamneseUndDiagnostik.Phaenotypisierung.ZeitraumSymptom.modifierExtension</t>
-  </si>
-  <si>
-    <t>Seltene.AnamneseUndDiagnostik.Phaenotypisierung.ZeitraumSymptom.ZeitraumSymptom</t>
+    <t>Seltene.anamneseUndDiagnostik.phaenotypisierung.zeitraumSymptom.id</t>
+  </si>
+  <si>
+    <t>Seltene.anamneseUndDiagnostik.phaenotypisierung.zeitraumSymptom.extension</t>
+  </si>
+  <si>
+    <t>Seltene.anamneseUndDiagnostik.phaenotypisierung.zeitraumSymptom.modifierExtension</t>
+  </si>
+  <si>
+    <t>Seltene.anamneseUndDiagnostik.phaenotypisierung.zeitraumSymptom.zeitraumSymptom</t>
   </si>
   <si>
     <t xml:space="preserve">dateTime
@@ -462,7 +462,7 @@
     <t>Startdatum und bei Bedarf Periode der ersten Symptome/Anzeichen.</t>
   </si>
   <si>
-    <t>Seltene.AnamneseUndDiagnostik.Phaenotypisierung.ZeitraumSymptom.Lebensphase</t>
+    <t>Seltene.anamneseUndDiagnostik.phaenotypisierung.zeitraumSymptom.lebensphase</t>
   </si>
   <si>
     <t>Lebensphase Symptom</t>
@@ -471,7 +471,7 @@
     <t>Lebensphase, in der das Symptom aufgetreten ist.</t>
   </si>
   <si>
-    <t>Seltene.AnamneseUndDiagnostik.Phaenotypisierung.ZeitraumSymptom.AlterSymptom</t>
+    <t>Seltene.anamneseUndDiagnostik.phaenotypisierung.zeitraumSymptom.alterSymptom</t>
   </si>
   <si>
     <t xml:space="preserve">integer
@@ -484,7 +484,7 @@
     <t>Alter beim Auftreten der ersten Symptome/Anzeichen.</t>
   </si>
   <si>
-    <t>Seltene.AnamneseUndDiagnostik.Phaenotypisierung.VerlaufSymptom</t>
+    <t>Seltene.anamneseUndDiagnostik.phaenotypisierung.verlaufSymptom</t>
   </si>
   <si>
     <t>Verlauf Symptom</t>
@@ -493,22 +493,22 @@
     <t>Aenderung des Verlaufs des Symptoms seit der vorherigen Untersuchung.</t>
   </si>
   <si>
-    <t>Seltene.AnamneseUndDiagnostik.KlinischeDiagnose</t>
+    <t>Seltene.anamneseUndDiagnostik.klinischeDiagnose</t>
   </si>
   <si>
     <t>Zeitraum der klinischen SE-Diagnose</t>
   </si>
   <si>
-    <t>Seltene.AnamneseUndDiagnostik.KlinischeDiagnose.id</t>
-  </si>
-  <si>
-    <t>Seltene.AnamneseUndDiagnostik.KlinischeDiagnose.extension</t>
-  </si>
-  <si>
-    <t>Seltene.AnamneseUndDiagnostik.KlinischeDiagnose.modifierExtension</t>
-  </si>
-  <si>
-    <t>Seltene.AnamneseUndDiagnostik.KlinischeDiagnose.ZeitpunktKlinischeDia</t>
+    <t>Seltene.anamneseUndDiagnostik.klinischeDiagnose.id</t>
+  </si>
+  <si>
+    <t>Seltene.anamneseUndDiagnostik.klinischeDiagnose.extension</t>
+  </si>
+  <si>
+    <t>Seltene.anamneseUndDiagnostik.klinischeDiagnose.modifierExtension</t>
+  </si>
+  <si>
+    <t>Seltene.anamneseUndDiagnostik.klinischeDiagnose.zeitpunktKlinischeDia</t>
   </si>
   <si>
     <t>Zeitpunkt klinische SE-Diagnose</t>
@@ -517,7 +517,7 @@
     <t>Auswahl der Altersangabe (Lebensphase) des Zeitpunktes der klinsichen SE-Diagnose.</t>
   </si>
   <si>
-    <t>Seltene.AnamneseUndDiagnostik.KlinischeDiagnose.FeststellungsdatumKlinischeDia</t>
+    <t>Seltene.anamneseUndDiagnostik.klinischeDiagnose.feststellungsdatumKlinischeDia</t>
   </si>
   <si>
     <t>Feststellungsdatum klinische SE-Diagnose</t>
@@ -526,7 +526,7 @@
     <t>Datum, an dem die klinische SE-Diagnose festgestellt wurde.</t>
   </si>
   <si>
-    <t>Seltene.AnamneseUndDiagnostik.KlinischeDiagnose.AlterKlinischeDia</t>
+    <t>Seltene.anamneseUndDiagnostik.klinischeDiagnose.alterKlinischeDia</t>
   </si>
   <si>
     <t>Alter bei klinischer SE-Diagnose</t>
@@ -535,22 +535,22 @@
     <t>Alter, in dem die klinische SE-Diagnose gestellt wurde.</t>
   </si>
   <si>
-    <t>Seltene.AnamneseUndDiagnostik.GenetischeDiagnose</t>
+    <t>Seltene.anamneseUndDiagnostik.genetischeDiagnose</t>
   </si>
   <si>
     <t>Zeitraum der genetischen SE-Diagnose</t>
   </si>
   <si>
-    <t>Seltene.AnamneseUndDiagnostik.GenetischeDiagnose.id</t>
-  </si>
-  <si>
-    <t>Seltene.AnamneseUndDiagnostik.GenetischeDiagnose.extension</t>
-  </si>
-  <si>
-    <t>Seltene.AnamneseUndDiagnostik.GenetischeDiagnose.modifierExtension</t>
-  </si>
-  <si>
-    <t>Seltene.AnamneseUndDiagnostik.GenetischeDiagnose.ZeitpunktGenDia</t>
+    <t>Seltene.anamneseUndDiagnostik.genetischeDiagnose.id</t>
+  </si>
+  <si>
+    <t>Seltene.anamneseUndDiagnostik.genetischeDiagnose.extension</t>
+  </si>
+  <si>
+    <t>Seltene.anamneseUndDiagnostik.genetischeDiagnose.modifierExtension</t>
+  </si>
+  <si>
+    <t>Seltene.anamneseUndDiagnostik.genetischeDiagnose.zeitpunktGenDia</t>
   </si>
   <si>
     <t>Zeitpunkt genetische SE-Diagnose</t>
@@ -559,7 +559,7 @@
     <t>Auswahl der Altersangabe (Lebensphase) des Zeitpunktes der genetischen SE-Diagnose.</t>
   </si>
   <si>
-    <t>Seltene.AnamneseUndDiagnostik.GenetischeDiagnose.FeststellungsdatumGenDia</t>
+    <t>Seltene.anamneseUndDiagnostik.genetischeDiagnose.feststellungsdatumGenDia</t>
   </si>
   <si>
     <t>Feststellungsdatum genetische SE-Diagnose</t>
@@ -568,7 +568,7 @@
     <t>Datum, an dem die genetische SE-Diagnose festgestellt wurde.</t>
   </si>
   <si>
-    <t>Seltene.AnamneseUndDiagnostik.GenetischeDiagnose.AlterGenDia</t>
+    <t>Seltene.anamneseUndDiagnostik.genetischeDiagnose.alterGenDia</t>
   </si>
   <si>
     <t>Alter bei genetischer SE-Diagnose</t>
@@ -577,7 +577,7 @@
     <t>Alter, in dem die genetische SE-Diagnose gestellt wurde.</t>
   </si>
   <si>
-    <t>Seltene.AnamneseUndDiagnostik.GenDiaFehlendePenetranz</t>
+    <t>Seltene.anamneseUndDiagnostik.genDiaFehlendePenetranz</t>
   </si>
   <si>
     <t>Genetische Diagnose mit fehlender Penetranz</t>
@@ -586,7 +586,7 @@
     <t>Gibt an, ob bei einer genetischen Diagnose die Penetranz (Wahrscheinlichkeit Genotyp bildet Phaenotyp aus) fehlt</t>
   </si>
   <si>
-    <t>Seltene.AnamneseUndDiagnostik.MethodeDiagnosestellung</t>
+    <t>Seltene.anamneseUndDiagnostik.methodeDiagnosestellung</t>
   </si>
   <si>
     <t>Methode der Diagnosestellung</t>
@@ -595,37 +595,37 @@
     <t>Gibt an, welche Methode zur Diagnosestellung verwendet wurde.</t>
   </si>
   <si>
-    <t>Seltene.KoerperlicheUntersuchung</t>
+    <t>Seltene.koerperlicheUntersuchung</t>
   </si>
   <si>
     <t>Körperliche Untersuchung</t>
   </si>
   <si>
-    <t>Seltene.KoerperlicheUntersuchung.id</t>
-  </si>
-  <si>
-    <t>Seltene.KoerperlicheUntersuchung.extension</t>
-  </si>
-  <si>
-    <t>Seltene.KoerperlicheUntersuchung.modifierExtension</t>
-  </si>
-  <si>
-    <t>Seltene.KoerperlicheUntersuchung.Koerpergewicht</t>
+    <t>Seltene.koerperlicheUntersuchung.id</t>
+  </si>
+  <si>
+    <t>Seltene.koerperlicheUntersuchung.extension</t>
+  </si>
+  <si>
+    <t>Seltene.koerperlicheUntersuchung.modifierExtension</t>
+  </si>
+  <si>
+    <t>Seltene.koerperlicheUntersuchung.koerpergewicht</t>
   </si>
   <si>
     <t>Körpergewicht</t>
   </si>
   <si>
-    <t>Seltene.KoerperlicheUntersuchung.Koerpergewicht.id</t>
-  </si>
-  <si>
-    <t>Seltene.KoerperlicheUntersuchung.Koerpergewicht.extension</t>
-  </si>
-  <si>
-    <t>Seltene.KoerperlicheUntersuchung.Koerpergewicht.modifierExtension</t>
-  </si>
-  <si>
-    <t>Seltene.KoerperlicheUntersuchung.Koerpergewicht.Koerpergewicht</t>
+    <t>Seltene.koerperlicheUntersuchung.koerpergewicht.id</t>
+  </si>
+  <si>
+    <t>Seltene.koerperlicheUntersuchung.koerpergewicht.extension</t>
+  </si>
+  <si>
+    <t>Seltene.koerperlicheUntersuchung.koerpergewicht.modifierExtension</t>
+  </si>
+  <si>
+    <t>Seltene.koerperlicheUntersuchung.koerpergewicht.koerpergewicht</t>
   </si>
   <si>
     <t xml:space="preserve">decimal
@@ -638,7 +638,7 @@
     <t>Körpergewicht des SE-Patienten in kg (aus MII ICU Modul).</t>
   </si>
   <si>
-    <t>Seltene.KoerperlicheUntersuchung.Koerpergewicht.DatumKoerpergewicht</t>
+    <t>Seltene.koerperlicheUntersuchung.koerpergewicht.datumKoerpergewicht</t>
   </si>
   <si>
     <t>Datum Körpergewicht</t>
@@ -647,22 +647,22 @@
     <t>Datum der Körpergewichtsmessung.</t>
   </si>
   <si>
-    <t>Seltene.KoerperlicheUntersuchung.Koerpergroesse</t>
+    <t>Seltene.koerperlicheUntersuchung.koerpergroesse</t>
   </si>
   <si>
     <t>Körpergröße</t>
   </si>
   <si>
-    <t>Seltene.KoerperlicheUntersuchung.Koerpergroesse.id</t>
-  </si>
-  <si>
-    <t>Seltene.KoerperlicheUntersuchung.Koerpergroesse.extension</t>
-  </si>
-  <si>
-    <t>Seltene.KoerperlicheUntersuchung.Koerpergroesse.modifierExtension</t>
-  </si>
-  <si>
-    <t>Seltene.KoerperlicheUntersuchung.Koerpergroesse.Koerpergroesse</t>
+    <t>Seltene.koerperlicheUntersuchung.koerpergroesse.id</t>
+  </si>
+  <si>
+    <t>Seltene.koerperlicheUntersuchung.koerpergroesse.extension</t>
+  </si>
+  <si>
+    <t>Seltene.koerperlicheUntersuchung.koerpergroesse.modifierExtension</t>
+  </si>
+  <si>
+    <t>Seltene.koerperlicheUntersuchung.koerpergroesse.koerpergroesse</t>
   </si>
   <si>
     <t>Körpergröße in cm</t>
@@ -671,7 +671,7 @@
     <t>Körpergröße des SE-Patienten in cm (aus MII ICU Modul).</t>
   </si>
   <si>
-    <t>Seltene.KoerperlicheUntersuchung.Koerpergroesse.DatumKoerpergroesse</t>
+    <t>Seltene.koerperlicheUntersuchung.koerpergroesse.datumKoerpergroesse</t>
   </si>
   <si>
     <t>Datum Körpergröße</t>
@@ -680,22 +680,22 @@
     <t>Datum der Körpergrößenmessung.</t>
   </si>
   <si>
-    <t>Seltene.KoerperlicheUntersuchung.BMI</t>
+    <t>Seltene.koerperlicheUntersuchung.bmi</t>
   </si>
   <si>
     <t>BMI</t>
   </si>
   <si>
-    <t>Seltene.KoerperlicheUntersuchung.BMI.id</t>
-  </si>
-  <si>
-    <t>Seltene.KoerperlicheUntersuchung.BMI.extension</t>
-  </si>
-  <si>
-    <t>Seltene.KoerperlicheUntersuchung.BMI.modifierExtension</t>
-  </si>
-  <si>
-    <t>Seltene.KoerperlicheUntersuchung.BMI.BMI</t>
+    <t>Seltene.koerperlicheUntersuchung.bmi.id</t>
+  </si>
+  <si>
+    <t>Seltene.koerperlicheUntersuchung.bmi.extension</t>
+  </si>
+  <si>
+    <t>Seltene.koerperlicheUntersuchung.bmi.modifierExtension</t>
+  </si>
+  <si>
+    <t>Seltene.koerperlicheUntersuchung.bmi.bmi</t>
   </si>
   <si>
     <t>BMI SE-Patient</t>
@@ -704,7 +704,7 @@
     <t>BMI des SE-Patienten.</t>
   </si>
   <si>
-    <t>Seltene.KoerperlicheUntersuchung.BMI.DatumBMI</t>
+    <t>Seltene.koerperlicheUntersuchung.bmi.datumBMI</t>
   </si>
   <si>
     <t>Datum des BMI</t>
@@ -713,22 +713,22 @@
     <t>Datum, an dem der BMI (Body Mass Index) berechnet wurde.</t>
   </si>
   <si>
-    <t>Seltene.KoerperlicheUntersuchung.Kopfumfang</t>
+    <t>Seltene.koerperlicheUntersuchung.kopfumfang</t>
   </si>
   <si>
     <t>Kopfumfang</t>
   </si>
   <si>
-    <t>Seltene.KoerperlicheUntersuchung.Kopfumfang.id</t>
-  </si>
-  <si>
-    <t>Seltene.KoerperlicheUntersuchung.Kopfumfang.extension</t>
-  </si>
-  <si>
-    <t>Seltene.KoerperlicheUntersuchung.Kopfumfang.modifierExtension</t>
-  </si>
-  <si>
-    <t>Seltene.KoerperlicheUntersuchung.Kopfumfang.Kopfumfang</t>
+    <t>Seltene.koerperlicheUntersuchung.kopfumfang.id</t>
+  </si>
+  <si>
+    <t>Seltene.koerperlicheUntersuchung.kopfumfang.extension</t>
+  </si>
+  <si>
+    <t>Seltene.koerperlicheUntersuchung.kopfumfang.modifierExtension</t>
+  </si>
+  <si>
+    <t>Seltene.koerperlicheUntersuchung.kopfumfang.kopfumfang</t>
   </si>
   <si>
     <t>Kopfumfang in cm</t>
@@ -737,7 +737,7 @@
     <t>Kopfumfang des SE-Patienten in cm.</t>
   </si>
   <si>
-    <t>Seltene.KoerperlicheUntersuchung.Kopfumfang.DatumKopfumfang</t>
+    <t>Seltene.koerperlicheUntersuchung.kopfumfang.datumKopfumfang</t>
   </si>
   <si>
     <t>Datum Kopfumfang</t>
@@ -746,22 +746,22 @@
     <t>Datum der Kopfumfangsmessung.</t>
   </si>
   <si>
-    <t>Seltene.KoerperlicheUntersuchung.Bauchumfang</t>
+    <t>Seltene.koerperlicheUntersuchung.bauchumfang</t>
   </si>
   <si>
     <t>Bauchumfang</t>
   </si>
   <si>
-    <t>Seltene.KoerperlicheUntersuchung.Bauchumfang.id</t>
-  </si>
-  <si>
-    <t>Seltene.KoerperlicheUntersuchung.Bauchumfang.extension</t>
-  </si>
-  <si>
-    <t>Seltene.KoerperlicheUntersuchung.Bauchumfang.modifierExtension</t>
-  </si>
-  <si>
-    <t>Seltene.KoerperlicheUntersuchung.Bauchumfang.Bauchumfang</t>
+    <t>Seltene.koerperlicheUntersuchung.bauchumfang.id</t>
+  </si>
+  <si>
+    <t>Seltene.koerperlicheUntersuchung.bauchumfang.extension</t>
+  </si>
+  <si>
+    <t>Seltene.koerperlicheUntersuchung.bauchumfang.modifierExtension</t>
+  </si>
+  <si>
+    <t>Seltene.koerperlicheUntersuchung.bauchumfang.bauchumfang</t>
   </si>
   <si>
     <t>Bauchumfang in cm</t>
@@ -770,7 +770,7 @@
     <t>Bauchumfang des SE-Patienten in cm.</t>
   </si>
   <si>
-    <t>Seltene.KoerperlicheUntersuchung.Bauchumfang.DatumBauchumfang</t>
+    <t>Seltene.koerperlicheUntersuchung.bauchumfang.datumBauchumfang</t>
   </si>
   <si>
     <t>Datum Bauchumfang</t>
@@ -779,22 +779,22 @@
     <t>Datum der Bauchumfangsmessung.</t>
   </si>
   <si>
-    <t>Seltene.KoerperlicheUntersuchung.Hueftumfang</t>
+    <t>Seltene.koerperlicheUntersuchung.hueftumfang</t>
   </si>
   <si>
     <t>Hüftumfang</t>
   </si>
   <si>
-    <t>Seltene.KoerperlicheUntersuchung.Hueftumfang.id</t>
-  </si>
-  <si>
-    <t>Seltene.KoerperlicheUntersuchung.Hueftumfang.extension</t>
-  </si>
-  <si>
-    <t>Seltene.KoerperlicheUntersuchung.Hueftumfang.modifierExtension</t>
-  </si>
-  <si>
-    <t>Seltene.KoerperlicheUntersuchung.Hueftumfang.Hueftumfang</t>
+    <t>Seltene.koerperlicheUntersuchung.hueftumfang.id</t>
+  </si>
+  <si>
+    <t>Seltene.koerperlicheUntersuchung.hueftumfang.extension</t>
+  </si>
+  <si>
+    <t>Seltene.koerperlicheUntersuchung.hueftumfang.modifierExtension</t>
+  </si>
+  <si>
+    <t>Seltene.koerperlicheUntersuchung.hueftumfang.hueftumfang</t>
   </si>
   <si>
     <t>Hüftumfang in cm</t>
@@ -803,7 +803,7 @@
     <t>Hüftumfang des SE-Patienten in cm.</t>
   </si>
   <si>
-    <t>Seltene.KoerperlicheUntersuchung.Hueftumfang.DatumHueftumfang</t>
+    <t>Seltene.koerperlicheUntersuchung.hueftumfang.datumHueftumfang</t>
   </si>
   <si>
     <t>Datum Hüftumfang</t>
@@ -812,7 +812,7 @@
     <t>Datum der Hüftumfangsmessung.</t>
   </si>
   <si>
-    <t>Seltene.KoerperlicheUntersuchung.Blutgruppe</t>
+    <t>Seltene.koerperlicheUntersuchung.blutgruppe</t>
   </si>
   <si>
     <t>Blutgruppe</t>
@@ -821,37 +821,37 @@
     <t>Blutgruppe des SE-Patienten (AB0 und Rhesusfaktor).</t>
   </si>
   <si>
-    <t>Seltene.PersoenlicheInfosIndexpatient</t>
+    <t>Seltene.persoenlicheInfosIndexpatient</t>
   </si>
   <si>
     <t>Persoenliche Informationen des Indexpatienten</t>
   </si>
   <si>
-    <t>Seltene.PersoenlicheInfosIndexpatient.id</t>
-  </si>
-  <si>
-    <t>Seltene.PersoenlicheInfosIndexpatient.extension</t>
-  </si>
-  <si>
-    <t>Seltene.PersoenlicheInfosIndexpatient.modifierExtension</t>
-  </si>
-  <si>
-    <t>Seltene.PersoenlicheInfosIndexpatient.Tod</t>
+    <t>Seltene.persoenlicheInfosIndexpatient.id</t>
+  </si>
+  <si>
+    <t>Seltene.persoenlicheInfosIndexpatient.extension</t>
+  </si>
+  <si>
+    <t>Seltene.persoenlicheInfosIndexpatient.modifierExtension</t>
+  </si>
+  <si>
+    <t>Seltene.persoenlicheInfosIndexpatient.tod</t>
   </si>
   <si>
     <t>Tod</t>
   </si>
   <si>
-    <t>Seltene.PersoenlicheInfosIndexpatient.Tod.id</t>
-  </si>
-  <si>
-    <t>Seltene.PersoenlicheInfosIndexpatient.Tod.extension</t>
-  </si>
-  <si>
-    <t>Seltene.PersoenlicheInfosIndexpatient.Tod.modifierExtension</t>
-  </si>
-  <si>
-    <t>Seltene.PersoenlicheInfosIndexpatient.Tod.Sterbedatum</t>
+    <t>Seltene.persoenlicheInfosIndexpatient.tod.id</t>
+  </si>
+  <si>
+    <t>Seltene.persoenlicheInfosIndexpatient.tod.extension</t>
+  </si>
+  <si>
+    <t>Seltene.persoenlicheInfosIndexpatient.tod.modifierExtension</t>
+  </si>
+  <si>
+    <t>Seltene.persoenlicheInfosIndexpatient.tod.sterbedatum</t>
   </si>
   <si>
     <t>Sterbedatum</t>
@@ -860,7 +860,7 @@
     <t>Sterbedatum des Indexpatienten.</t>
   </si>
   <si>
-    <t>Seltene.PersoenlicheInfosIndexpatient.Tod.AnSEVerstorben</t>
+    <t>Seltene.persoenlicheInfosIndexpatient.tod.anSEVerstorben</t>
   </si>
   <si>
     <t>An der SE verstorben</t>
@@ -869,7 +869,7 @@
     <t>Angabe, ob der Indexpatient an der SE verstorben ist.</t>
   </si>
   <si>
-    <t>Seltene.PersoenlicheInfosIndexpatient.Tod.AndereTodesursache</t>
+    <t>Seltene.persoenlicheInfosIndexpatient.tod.andereTodesursache</t>
   </si>
   <si>
     <t>Todesursache</t>
@@ -878,22 +878,22 @@
     <t>Kodierung der Todesursache soweit bekannt (ICD-10-GM, ORPHAcodes).</t>
   </si>
   <si>
-    <t>Seltene.Familienanamnese</t>
+    <t>Seltene.familienanamnese</t>
   </si>
   <si>
     <t>Familienanamnese</t>
   </si>
   <si>
-    <t>Seltene.Familienanamnese.id</t>
-  </si>
-  <si>
-    <t>Seltene.Familienanamnese.extension</t>
-  </si>
-  <si>
-    <t>Seltene.Familienanamnese.modifierExtension</t>
-  </si>
-  <si>
-    <t>Seltene.Familienanamnese.Verwandtschaftsverhaeltnis</t>
+    <t>Seltene.familienanamnese.id</t>
+  </si>
+  <si>
+    <t>Seltene.familienanamnese.extension</t>
+  </si>
+  <si>
+    <t>Seltene.familienanamnese.modifierExtension</t>
+  </si>
+  <si>
+    <t>Seltene.familienanamnese.verwandtschaftsverhaeltnis</t>
   </si>
   <si>
     <t>Verwandtschaftsverhaeltnis</t>
@@ -902,7 +902,7 @@
     <t>Biologisches Verwandtschaftsverhaeltnis des Familienmitglieds zum Indexpatienten.</t>
   </si>
   <si>
-    <t>Seltene.Familienanamnese.Geschlecht</t>
+    <t>Seltene.familienanamnese.geschlecht</t>
   </si>
   <si>
     <t>Geschlecht</t>
@@ -911,7 +911,7 @@
     <t>Geschlecht des Familienmitglieds.</t>
   </si>
   <si>
-    <t>Seltene.Familienanamnese.GleicheSE</t>
+    <t>Seltene.familienanamnese.gleicheSE</t>
   </si>
   <si>
     <t>Gleiche SE</t>
@@ -920,7 +920,7 @@
     <t>Gibt an, ob das Familienmitglied an der gleichen SE leidet wie der Indexpatient.</t>
   </si>
   <si>
-    <t>Seltene.Familienanamnese.AndereSE</t>
+    <t>Seltene.familienanamnese.andereSE</t>
   </si>
   <si>
     <t>Andere SE</t>
@@ -929,7 +929,7 @@
     <t>Gibt an, ob das Familienmitglied an einer anderen SE leidet als der Indexpatient.</t>
   </si>
   <si>
-    <t>Seltene.Familienanamnese.Penetranz</t>
+    <t>Seltene.familienanamnese.penetranz</t>
   </si>
   <si>
     <t>Penetranz</t>
@@ -938,7 +938,7 @@
     <t>Gibt an, ob bei fehlender klinscher Penetranz (Wahrscheinlichkeit Genotyp bildet Phaenotyp aus) die genetische Diagnose vorliegt.</t>
   </si>
   <si>
-    <t>Seltene.Familienanamnese.FamilienmitgliedVerstorben</t>
+    <t>Seltene.familienanamnese.familienmitgliedVerstorben</t>
   </si>
   <si>
     <t>Familienmitglied verstorben</t>
@@ -947,43 +947,43 @@
     <t>Gibt an, ob das Familienmitglied verstorben ist.</t>
   </si>
   <si>
-    <t>Seltene.TherapieForschung</t>
+    <t>Seltene.therapieForschung</t>
   </si>
   <si>
     <t>Therapie und Forschung</t>
   </si>
   <si>
-    <t>Seltene.TherapieForschung.id</t>
-  </si>
-  <si>
-    <t>Seltene.TherapieForschung.extension</t>
-  </si>
-  <si>
-    <t>Seltene.TherapieForschung.modifierExtension</t>
-  </si>
-  <si>
-    <t>Seltene.TherapieForschung.OffLabel</t>
+    <t>Seltene.therapieForschung.id</t>
+  </si>
+  <si>
+    <t>Seltene.therapieForschung.extension</t>
+  </si>
+  <si>
+    <t>Seltene.therapieForschung.modifierExtension</t>
+  </si>
+  <si>
+    <t>Seltene.therapieForschung.offLabel</t>
   </si>
   <si>
     <t>Off-Label-Gabe</t>
   </si>
   <si>
-    <t>Seltene.TherapieForschung.OffLabel.id</t>
-  </si>
-  <si>
-    <t>Seltene.TherapieForschung.OffLabel.extension</t>
-  </si>
-  <si>
-    <t>Seltene.TherapieForschung.OffLabel.modifierExtension</t>
-  </si>
-  <si>
-    <t>Seltene.TherapieForschung.OffLabel.OffLabelGabe</t>
+    <t>Seltene.therapieForschung.offLabel.id</t>
+  </si>
+  <si>
+    <t>Seltene.therapieForschung.offLabel.extension</t>
+  </si>
+  <si>
+    <t>Seltene.therapieForschung.offLabel.modifierExtension</t>
+  </si>
+  <si>
+    <t>Seltene.therapieForschung.offLabel.offLabelGabe</t>
   </si>
   <si>
     <t>Gibt an, ob eine Off-Label-Gabe vorliegt.</t>
   </si>
   <si>
-    <t>Seltene.TherapieForschung.OffLabel.OffLabelMedikament</t>
+    <t>Seltene.therapieForschung.offLabel.offLabelMedikament</t>
   </si>
   <si>
     <t>Off-Label-Medikament</t>
@@ -992,22 +992,22 @@
     <t>Gibt an, welches Medikament Off-Label gegeben wurde.</t>
   </si>
   <si>
-    <t>Seltene.TherapieForschung.Studie</t>
+    <t>Seltene.therapieForschung.studie</t>
   </si>
   <si>
     <t>Studie</t>
   </si>
   <si>
-    <t>Seltene.TherapieForschung.Studie.id</t>
-  </si>
-  <si>
-    <t>Seltene.TherapieForschung.Studie.extension</t>
-  </si>
-  <si>
-    <t>Seltene.TherapieForschung.Studie.modifierExtension</t>
-  </si>
-  <si>
-    <t>Seltene.TherapieForschung.Studie.StudienID</t>
+    <t>Seltene.therapieForschung.studie.id</t>
+  </si>
+  <si>
+    <t>Seltene.therapieForschung.studie.extension</t>
+  </si>
+  <si>
+    <t>Seltene.therapieForschung.studie.modifierExtension</t>
+  </si>
+  <si>
+    <t>Seltene.therapieForschung.studie.studienID</t>
   </si>
   <si>
     <t xml:space="preserve">Identifier
@@ -1020,7 +1020,7 @@
     <t>Eindeutige Identifikation der Studie, an der der SE-Patient teilgenommen hat.</t>
   </si>
   <si>
-    <t>Seltene.TherapieForschung.Studie.StudienStatus</t>
+    <t>Seltene.therapieForschung.studie.studienStatus</t>
   </si>
   <si>
     <t>Studienstatus</t>
@@ -1029,7 +1029,7 @@
     <t>Aktueller Status der Studie, an der der SE-Patient teilgenommen hat (Abgeschlossen, Fortlaufend).</t>
   </si>
   <si>
-    <t>Seltene.TherapieForschung.Studie.Studienzeitraum</t>
+    <t>Seltene.therapieForschung.studie.studienzeitraum</t>
   </si>
   <si>
     <t xml:space="preserve">Extension {organization-period}
@@ -1042,22 +1042,22 @@
     <t>Zeitraum, in dem der SE-Patient an der Studie teilgenommen hat.</t>
   </si>
   <si>
-    <t>Seltene.TherapieForschung.Therapie</t>
+    <t>Seltene.therapieForschung.therapie</t>
   </si>
   <si>
     <t>Therapie</t>
   </si>
   <si>
-    <t>Seltene.TherapieForschung.Therapie.id</t>
-  </si>
-  <si>
-    <t>Seltene.TherapieForschung.Therapie.extension</t>
-  </si>
-  <si>
-    <t>Seltene.TherapieForschung.Therapie.modifierExtension</t>
-  </si>
-  <si>
-    <t>Seltene.TherapieForschung.Therapie.Therapieempfehlung</t>
+    <t>Seltene.therapieForschung.therapie.id</t>
+  </si>
+  <si>
+    <t>Seltene.therapieForschung.therapie.extension</t>
+  </si>
+  <si>
+    <t>Seltene.therapieForschung.therapie.modifierExtension</t>
+  </si>
+  <si>
+    <t>Seltene.therapieForschung.therapie.therapieempfehlung</t>
   </si>
   <si>
     <t>Eine Therapieempfehlung beschreibt eine spezifische Maßnahme oder Strategie. Sie kann eigenständig vorliegen oder referenziert einem Therapieplan zugeordnet werden. Art der Therapieempfehlung</t>
@@ -1066,7 +1066,7 @@
     <t>Gibt an, welche Therapieempfehlung vorliegt.</t>
   </si>
   <si>
-    <t>Seltene.TherapieForschung.Therapie.DurchgefuehrteTherapie</t>
+    <t>Seltene.therapieForschung.therapie.durchgefuehrteTherapie</t>
   </si>
   <si>
     <t>Durchgefuehrte Therapie</t>
@@ -1075,7 +1075,7 @@
     <t>Tatsaechlich durchgeführte Therapie des SE-Patienten (mit oder ohne Studie mit heilender Intention).</t>
   </si>
   <si>
-    <t>Seltene.TherapieForschung.Therapie.StartdatumTherapie</t>
+    <t>Seltene.therapieForschung.therapie.startdatumTherapie</t>
   </si>
   <si>
     <t>Startdatum Therapie</t>
@@ -1084,7 +1084,7 @@
     <t>Datum, an dem die Therapie begonnen hat.</t>
   </si>
   <si>
-    <t>Seltene.TherapieForschung.Therapie.EnddatumTherapie</t>
+    <t>Seltene.therapieForschung.therapie.enddatumTherapie</t>
   </si>
   <si>
     <t>Enddatum Therapie</t>
@@ -1093,7 +1093,7 @@
     <t>Datum, an dem die Therapie beendet wurde.</t>
   </si>
   <si>
-    <t>Seltene.TherapieForschung.Therapie.GrundEndeTherapie</t>
+    <t>Seltene.therapieForschung.therapie.grundEndeTherapie</t>
   </si>
   <si>
     <t>Grund Ende Therapie</t>
@@ -1404,8 +1404,8 @@
   <dimension ref="A1:AJ130"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="72.91796875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="72.91796875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="72.3515625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="72.3515625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="18.19140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -1435,7 +1435,7 @@
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="72.91796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="72.3515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-lm-seltene.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-lm-seltene.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4130" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4192" uniqueCount="362">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T14:14:40+00:00</t>
+    <t>2026-09-02T14:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -945,6 +945,24 @@
   </si>
   <si>
     <t>Gibt an, ob das Familienmitglied verstorben ist.</t>
+  </si>
+  <si>
+    <t>Seltene.familienanamnese.todDurchSE</t>
+  </si>
+  <si>
+    <t>Tod durch seltene Erkrankung</t>
+  </si>
+  <si>
+    <t>Gibt an, ob die seltene Erkrankung zum Tod des Familienmitglieds beigetragen hat. Abzugrenzen von familienmitgliedVerstorben, das nur den Tod als solchen festhaelt.</t>
+  </si>
+  <si>
+    <t>Seltene.familienanamnese.dokumentationsdatum</t>
+  </si>
+  <si>
+    <t>Dokumentationsdatum</t>
+  </si>
+  <si>
+    <t>Datum, an dem die Familienanamnese erhoben beziehungsweise dokumentiert wurde.</t>
   </si>
   <si>
     <t>Seltene.therapieForschung</t>
@@ -1401,7 +1419,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ130"/>
+  <dimension ref="A1:AJ132"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="72.3515625" customWidth="true" bestFit="true"/>
@@ -11959,7 +11977,7 @@
         <v>74</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>73</v>
@@ -11971,13 +11989,13 @@
         <v>73</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="L105" t="s" s="2">
         <v>306</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -12034,21 +12052,21 @@
         <v>74</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12071,13 +12089,13 @@
         <v>73</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>83</v>
+        <v>309</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>84</v>
+        <v>310</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -12128,7 +12146,7 @@
         <v>73</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>85</v>
+        <v>308</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>74</v>
@@ -12145,14 +12163,14 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
@@ -12171,17 +12189,15 @@
         <v>73</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>89</v>
+        <v>312</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>91</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="N107" s="2"/>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>73</v>
@@ -12218,19 +12234,19 @@
         <v>73</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="AC107" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AD107" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>95</v>
+        <v>311</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>74</v>
@@ -12242,51 +12258,47 @@
         <v>73</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>96</v>
+        <v>79</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H108" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I108" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="O108" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="N108" s="2"/>
+      <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>73</v>
       </c>
@@ -12334,31 +12346,31 @@
         <v>73</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI108" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
@@ -12377,15 +12389,17 @@
         <v>73</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>311</v>
+        <v>89</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="N109" s="2"/>
+        <v>90</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>91</v>
+      </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>73</v>
@@ -12422,19 +12436,19 @@
         <v>73</v>
       </c>
       <c r="AB109" t="s" s="2">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="AC109" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AD109" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE109" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>310</v>
+        <v>95</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>74</v>
@@ -12446,47 +12460,51 @@
         <v>73</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>79</v>
+        <v>96</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I110" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="N110" s="2"/>
-      <c r="O110" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="O110" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="P110" t="s" s="2">
         <v>73</v>
       </c>
@@ -12534,31 +12552,31 @@
         <v>73</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
@@ -12577,17 +12595,15 @@
         <v>73</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>89</v>
+        <v>317</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>91</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="N111" s="2"/>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>73</v>
@@ -12624,19 +12640,19 @@
         <v>73</v>
       </c>
       <c r="AB111" t="s" s="2">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="AC111" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AD111" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE111" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>95</v>
+        <v>316</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>74</v>
@@ -12648,51 +12664,47 @@
         <v>73</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>96</v>
+        <v>79</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H112" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I112" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="N112" s="2"/>
+      <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>73</v>
       </c>
@@ -12740,38 +12752,38 @@
         <v>73</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>73</v>
@@ -12783,15 +12795,17 @@
         <v>73</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>311</v>
+        <v>89</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N113" s="2"/>
+        <v>90</v>
+      </c>
+      <c r="N113" t="s" s="2">
+        <v>91</v>
+      </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>73</v>
@@ -12828,43 +12842,43 @@
         <v>73</v>
       </c>
       <c r="AB113" t="s" s="2">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="AC113" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AD113" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE113" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>315</v>
+        <v>95</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
@@ -12877,22 +12891,26 @@
         <v>73</v>
       </c>
       <c r="I114" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J114" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>318</v>
+        <v>105</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="N114" s="2"/>
-      <c r="O114" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="O114" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="P114" t="s" s="2">
         <v>73</v>
       </c>
@@ -12940,7 +12958,7 @@
         <v>73</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>317</v>
+        <v>108</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>74</v>
@@ -12952,15 +12970,15 @@
         <v>73</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -12971,7 +12989,7 @@
         <v>74</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>73</v>
@@ -12983,13 +13001,13 @@
         <v>73</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -13040,27 +13058,27 @@
         <v>73</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -13071,7 +13089,7 @@
         <v>74</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>73</v>
@@ -13083,13 +13101,13 @@
         <v>73</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>83</v>
+        <v>324</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>84</v>
+        <v>325</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -13140,13 +13158,13 @@
         <v>73</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>85</v>
+        <v>323</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI116" t="s" s="2">
         <v>73</v>
@@ -13157,14 +13175,14 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
@@ -13183,17 +13201,15 @@
         <v>73</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>89</v>
+        <v>327</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>91</v>
-      </c>
+        <v>327</v>
+      </c>
+      <c r="N117" s="2"/>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
         <v>73</v>
@@ -13230,19 +13246,19 @@
         <v>73</v>
       </c>
       <c r="AB117" t="s" s="2">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="AC117" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AD117" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE117" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>95</v>
+        <v>326</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>74</v>
@@ -13254,51 +13270,47 @@
         <v>73</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>96</v>
+        <v>79</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G118" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H118" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I118" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="O118" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="N118" s="2"/>
+      <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>73</v>
       </c>
@@ -13346,38 +13358,38 @@
         <v>73</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI118" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H119" t="s" s="2">
         <v>73</v>
@@ -13389,15 +13401,17 @@
         <v>73</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>326</v>
+        <v>88</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>327</v>
+        <v>89</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="N119" s="2"/>
+        <v>90</v>
+      </c>
+      <c r="N119" t="s" s="2">
+        <v>91</v>
+      </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>73</v>
@@ -13434,71 +13448,75 @@
         <v>73</v>
       </c>
       <c r="AB119" t="s" s="2">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="AC119" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AD119" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE119" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>325</v>
+        <v>95</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI119" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H120" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I120" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J120" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>330</v>
+        <v>105</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="N120" s="2"/>
-      <c r="O120" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="N120" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="O120" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="P120" t="s" s="2">
         <v>73</v>
       </c>
@@ -13546,27 +13564,27 @@
         <v>73</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>329</v>
+        <v>108</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH120" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI120" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ120" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -13589,13 +13607,13 @@
         <v>73</v>
       </c>
       <c r="K121" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="L121" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="L121" t="s" s="2">
+      <c r="M121" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="M121" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -13646,7 +13664,7 @@
         <v>73</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>74</v>
@@ -13663,10 +13681,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -13677,7 +13695,7 @@
         <v>74</v>
       </c>
       <c r="G122" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H122" t="s" s="2">
         <v>73</v>
@@ -13689,10 +13707,10 @@
         <v>73</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="M122" t="s" s="2">
         <v>337</v>
@@ -13746,19 +13764,19 @@
         <v>73</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH122" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI122" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="123">
@@ -13789,13 +13807,13 @@
         <v>73</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>82</v>
+        <v>339</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>83</v>
+        <v>340</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>84</v>
+        <v>341</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -13846,7 +13864,7 @@
         <v>73</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>85</v>
+        <v>338</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>74</v>
@@ -13863,14 +13881,14 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
@@ -13889,17 +13907,15 @@
         <v>73</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>89</v>
+        <v>343</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>91</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="N124" s="2"/>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
         <v>73</v>
@@ -13936,19 +13952,19 @@
         <v>73</v>
       </c>
       <c r="AB124" t="s" s="2">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="AC124" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AD124" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE124" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>95</v>
+        <v>342</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>74</v>
@@ -13960,51 +13976,47 @@
         <v>73</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>96</v>
+        <v>79</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G125" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H125" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I125" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="J125" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="O125" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="N125" s="2"/>
+      <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
         <v>73</v>
       </c>
@@ -14052,31 +14064,31 @@
         <v>73</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH125" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI125" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
@@ -14095,15 +14107,17 @@
         <v>73</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>342</v>
+        <v>89</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="N126" s="2"/>
+        <v>90</v>
+      </c>
+      <c r="N126" t="s" s="2">
+        <v>91</v>
+      </c>
       <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
         <v>73</v>
@@ -14140,19 +14154,19 @@
         <v>73</v>
       </c>
       <c r="AB126" t="s" s="2">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="AC126" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AD126" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE126" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>341</v>
+        <v>95</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>74</v>
@@ -14164,19 +14178,19 @@
         <v>73</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
@@ -14189,22 +14203,26 @@
         <v>73</v>
       </c>
       <c r="I127" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J127" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>345</v>
+        <v>105</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N127" s="2"/>
-      <c r="O127" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="N127" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="O127" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="P127" t="s" s="2">
         <v>73</v>
       </c>
@@ -14252,7 +14270,7 @@
         <v>73</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>344</v>
+        <v>108</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>74</v>
@@ -14264,7 +14282,7 @@
         <v>73</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
     </row>
     <row r="128">
@@ -14283,7 +14301,7 @@
         <v>74</v>
       </c>
       <c r="G128" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H128" t="s" s="2">
         <v>73</v>
@@ -14295,7 +14313,7 @@
         <v>73</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="L128" t="s" s="2">
         <v>348</v>
@@ -14358,7 +14376,7 @@
         <v>74</v>
       </c>
       <c r="AH128" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI128" t="s" s="2">
         <v>73</v>
@@ -14383,7 +14401,7 @@
         <v>74</v>
       </c>
       <c r="G129" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H129" t="s" s="2">
         <v>73</v>
@@ -14395,7 +14413,7 @@
         <v>73</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="L129" t="s" s="2">
         <v>351</v>
@@ -14458,7 +14476,7 @@
         <v>74</v>
       </c>
       <c r="AH129" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI129" t="s" s="2">
         <v>73</v>
@@ -14483,7 +14501,7 @@
         <v>74</v>
       </c>
       <c r="G130" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H130" t="s" s="2">
         <v>73</v>
@@ -14495,7 +14513,7 @@
         <v>73</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="L130" t="s" s="2">
         <v>354</v>
@@ -14558,12 +14576,212 @@
         <v>74</v>
       </c>
       <c r="AH130" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI130" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ130" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="B131" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="C131" s="2"/>
+      <c r="D131" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E131" s="2"/>
+      <c r="F131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H131" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I131" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J131" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K131" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L131" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="M131" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="N131" s="2"/>
+      <c r="O131" s="2"/>
+      <c r="P131" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q131" s="2"/>
+      <c r="R131" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S131" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T131" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U131" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V131" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W131" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X131" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y131" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z131" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA131" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB131" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC131" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD131" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE131" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF131" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AG131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI131" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ131" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="B132" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="C132" s="2"/>
+      <c r="D132" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E132" s="2"/>
+      <c r="F132" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G132" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AI130" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ130" t="s" s="2">
+      <c r="H132" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I132" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J132" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K132" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L132" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="M132" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="N132" s="2"/>
+      <c r="O132" s="2"/>
+      <c r="P132" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q132" s="2"/>
+      <c r="R132" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S132" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T132" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U132" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V132" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W132" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X132" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y132" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z132" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA132" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB132" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC132" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD132" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE132" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF132" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="AG132" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH132" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI132" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ132" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-lm-seltene.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-lm-seltene.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4192" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4381" uniqueCount="373">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T14:33:43+00:00</t>
+    <t>2026-09-02T15:16:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -777,6 +777,39 @@
   </si>
   <si>
     <t>Datum der Bauchumfangsmessung.</t>
+  </si>
+  <si>
+    <t>Seltene.koerperlicheUntersuchung.taillenumfang</t>
+  </si>
+  <si>
+    <t>Taillenumfang</t>
+  </si>
+  <si>
+    <t>Seltene.koerperlicheUntersuchung.taillenumfang.id</t>
+  </si>
+  <si>
+    <t>Seltene.koerperlicheUntersuchung.taillenumfang.extension</t>
+  </si>
+  <si>
+    <t>Seltene.koerperlicheUntersuchung.taillenumfang.modifierExtension</t>
+  </si>
+  <si>
+    <t>Seltene.koerperlicheUntersuchung.taillenumfang.taillenumfang</t>
+  </si>
+  <si>
+    <t>Taillenumfang in cm</t>
+  </si>
+  <si>
+    <t>Taillenumfang des SE-Patienten in cm. Abzugrenzen vom Bauchumfang, der auf Nabelhoehe gemessen wird.</t>
+  </si>
+  <si>
+    <t>Seltene.koerperlicheUntersuchung.taillenumfang.datumTaillenumfang</t>
+  </si>
+  <si>
+    <t>Datum Taillenumfang</t>
+  </si>
+  <si>
+    <t>Datum der Taillenumfangsmessung.</t>
   </si>
   <si>
     <t>Seltene.koerperlicheUntersuchung.hueftumfang</t>
@@ -1419,7 +1452,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ132"/>
+  <dimension ref="A1:AJ138"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="72.3515625" customWidth="true" bestFit="true"/>
@@ -9759,7 +9792,7 @@
         <v>74</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>73</v>
@@ -9771,13 +9804,13 @@
         <v>73</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="L83" t="s" s="2">
         <v>261</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -9834,21 +9867,21 @@
         <v>74</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -9859,7 +9892,7 @@
         <v>74</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>73</v>
@@ -9871,13 +9904,13 @@
         <v>73</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>264</v>
+        <v>83</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>264</v>
+        <v>84</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -9928,38 +9961,38 @@
         <v>73</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>263</v>
+        <v>85</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>73</v>
@@ -9971,15 +10004,17 @@
         <v>73</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="N85" s="2"/>
+        <v>90</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>91</v>
+      </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>73</v>
@@ -10016,43 +10051,43 @@
         <v>73</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="AC85" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AD85" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -10065,24 +10100,26 @@
         <v>73</v>
       </c>
       <c r="I86" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="K86" t="s" s="2">
         <v>88</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="N86" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="O86" s="2"/>
+      <c r="O86" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="P86" t="s" s="2">
         <v>73</v>
       </c>
@@ -10118,19 +10155,19 @@
         <v>73</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>74</v>
@@ -10147,46 +10184,42 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>88</v>
+        <v>199</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>105</v>
+        <v>266</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>267</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>73</v>
       </c>
@@ -10234,19 +10267,19 @@
         <v>73</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>108</v>
+        <v>265</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
     </row>
     <row r="88">
@@ -10277,13 +10310,13 @@
         <v>73</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>98</v>
+        <v>141</v>
       </c>
       <c r="L88" t="s" s="2">
         <v>269</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -10346,15 +10379,15 @@
         <v>73</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10377,13 +10410,13 @@
         <v>73</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>83</v>
+        <v>272</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>84</v>
+        <v>273</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -10434,7 +10467,7 @@
         <v>73</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>85</v>
+        <v>271</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>74</v>
@@ -10451,14 +10484,14 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -10477,17 +10510,15 @@
         <v>73</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>89</v>
+        <v>275</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>91</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="N90" s="2"/>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>73</v>
@@ -10524,19 +10555,19 @@
         <v>73</v>
       </c>
       <c r="AB90" t="s" s="2">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="AC90" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AD90" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>95</v>
+        <v>274</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>74</v>
@@ -10548,51 +10579,47 @@
         <v>73</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>96</v>
+        <v>79</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I91" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="N91" s="2"/>
+      <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>73</v>
       </c>
@@ -10640,38 +10667,38 @@
         <v>73</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>73</v>
@@ -10683,15 +10710,17 @@
         <v>73</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>274</v>
+        <v>89</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N92" s="2"/>
+        <v>90</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>91</v>
+      </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>73</v>
@@ -10728,71 +10757,75 @@
         <v>73</v>
       </c>
       <c r="AB92" t="s" s="2">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="AC92" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AD92" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE92" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>273</v>
+        <v>95</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I93" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>277</v>
+        <v>105</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="N93" s="2"/>
-      <c r="O93" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="O93" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="P93" t="s" s="2">
         <v>73</v>
       </c>
@@ -10840,19 +10873,19 @@
         <v>73</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>276</v>
+        <v>108</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
     </row>
     <row r="94">
@@ -10871,7 +10904,7 @@
         <v>74</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>73</v>
@@ -10883,13 +10916,13 @@
         <v>73</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="L94" t="s" s="2">
         <v>280</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -10946,21 +10979,21 @@
         <v>74</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -10971,7 +11004,7 @@
         <v>74</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>73</v>
@@ -10983,13 +11016,13 @@
         <v>73</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>283</v>
+        <v>83</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>283</v>
+        <v>84</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -11040,38 +11073,38 @@
         <v>73</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>282</v>
+        <v>85</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>73</v>
@@ -11083,15 +11116,17 @@
         <v>73</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="N96" s="2"/>
+        <v>90</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>91</v>
+      </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>73</v>
@@ -11128,43 +11163,43 @@
         <v>73</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AD96" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -11177,24 +11212,26 @@
         <v>73</v>
       </c>
       <c r="I97" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="K97" t="s" s="2">
         <v>88</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="N97" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="O97" s="2"/>
+      <c r="O97" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="P97" t="s" s="2">
         <v>73</v>
       </c>
@@ -11230,19 +11267,19 @@
         <v>73</v>
       </c>
       <c r="AB97" t="s" s="2">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="AC97" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AD97" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>74</v>
@@ -11259,46 +11296,42 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I98" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>105</v>
+        <v>285</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>286</v>
+      </c>
+      <c r="N98" s="2"/>
+      <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>73</v>
       </c>
@@ -11346,19 +11379,19 @@
         <v>73</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>108</v>
+        <v>284</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
     </row>
     <row r="99">
@@ -11477,7 +11510,7 @@
         <v>74</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>73</v>
@@ -11552,7 +11585,7 @@
         <v>74</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>73</v>
@@ -11589,13 +11622,13 @@
         <v>73</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="L101" t="s" s="2">
         <v>294</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -11658,15 +11691,15 @@
         <v>73</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -11677,7 +11710,7 @@
         <v>74</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>73</v>
@@ -11689,13 +11722,13 @@
         <v>73</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>297</v>
+        <v>83</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>298</v>
+        <v>84</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -11746,13 +11779,13 @@
         <v>73</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>296</v>
+        <v>85</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>73</v>
@@ -11763,21 +11796,21 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>73</v>
@@ -11789,15 +11822,17 @@
         <v>73</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>300</v>
+        <v>89</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N103" s="2"/>
+        <v>90</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>91</v>
+      </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>73</v>
@@ -11834,71 +11869,75 @@
         <v>73</v>
       </c>
       <c r="AB103" t="s" s="2">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="AC103" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AD103" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE103" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>299</v>
+        <v>95</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I104" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>303</v>
+        <v>105</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N104" s="2"/>
-      <c r="O104" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="O104" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="P104" t="s" s="2">
         <v>73</v>
       </c>
@@ -11946,27 +11985,27 @@
         <v>73</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>302</v>
+        <v>108</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -11992,10 +12031,10 @@
         <v>114</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -12046,7 +12085,7 @@
         <v>73</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>74</v>
@@ -12063,10 +12102,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12089,13 +12128,13 @@
         <v>73</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -12146,7 +12185,7 @@
         <v>73</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>74</v>
@@ -12163,10 +12202,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12189,13 +12228,13 @@
         <v>73</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -12246,7 +12285,7 @@
         <v>73</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>74</v>
@@ -12258,15 +12297,15 @@
         <v>73</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12277,7 +12316,7 @@
         <v>74</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H108" t="s" s="2">
         <v>73</v>
@@ -12289,13 +12328,13 @@
         <v>73</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>83</v>
+        <v>308</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>84</v>
+        <v>309</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -12346,13 +12385,13 @@
         <v>73</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>85</v>
+        <v>307</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI108" t="s" s="2">
         <v>73</v>
@@ -12363,21 +12402,21 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>73</v>
@@ -12389,17 +12428,15 @@
         <v>73</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>89</v>
+        <v>311</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>91</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="N109" s="2"/>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>73</v>
@@ -12436,75 +12473,71 @@
         <v>73</v>
       </c>
       <c r="AB109" t="s" s="2">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="AC109" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AD109" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE109" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>95</v>
+        <v>310</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I110" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>105</v>
+        <v>314</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="N110" s="2"/>
+      <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>73</v>
       </c>
@@ -12552,19 +12585,19 @@
         <v>73</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>108</v>
+        <v>313</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
     </row>
     <row r="111">
@@ -12583,7 +12616,7 @@
         <v>74</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>73</v>
@@ -12595,13 +12628,13 @@
         <v>73</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="L111" t="s" s="2">
         <v>317</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -12658,21 +12691,21 @@
         <v>74</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -12695,13 +12728,13 @@
         <v>73</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>83</v>
+        <v>320</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>84</v>
+        <v>321</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -12752,7 +12785,7 @@
         <v>73</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>85</v>
+        <v>319</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>74</v>
@@ -12769,14 +12802,14 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
@@ -12795,17 +12828,15 @@
         <v>73</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>89</v>
+        <v>323</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>91</v>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="N113" s="2"/>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>73</v>
@@ -12842,19 +12873,19 @@
         <v>73</v>
       </c>
       <c r="AB113" t="s" s="2">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="AC113" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AD113" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE113" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>95</v>
+        <v>322</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>74</v>
@@ -12866,51 +12897,47 @@
         <v>73</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>96</v>
+        <v>79</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I114" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="J114" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="O114" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="N114" s="2"/>
+      <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
         <v>73</v>
       </c>
@@ -12958,38 +12985,38 @@
         <v>73</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>73</v>
@@ -13001,15 +13028,17 @@
         <v>73</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>317</v>
+        <v>89</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="N115" s="2"/>
+        <v>90</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>91</v>
+      </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
         <v>73</v>
@@ -13046,43 +13075,43 @@
         <v>73</v>
       </c>
       <c r="AB115" t="s" s="2">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="AC115" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AD115" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE115" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>321</v>
+        <v>95</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
@@ -13095,22 +13124,26 @@
         <v>73</v>
       </c>
       <c r="I116" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J116" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>324</v>
+        <v>105</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N116" s="2"/>
-      <c r="O116" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="N116" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="O116" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="P116" t="s" s="2">
         <v>73</v>
       </c>
@@ -13158,7 +13191,7 @@
         <v>73</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>323</v>
+        <v>108</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>74</v>
@@ -13170,15 +13203,15 @@
         <v>73</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -13204,10 +13237,10 @@
         <v>98</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -13258,7 +13291,7 @@
         <v>73</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>74</v>
@@ -13275,10 +13308,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -13375,10 +13408,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -13477,10 +13510,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -13581,10 +13614,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -13607,13 +13640,13 @@
         <v>73</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>332</v>
+        <v>114</v>
       </c>
       <c r="L121" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="M121" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="M121" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -13664,7 +13697,7 @@
         <v>73</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>74</v>
@@ -13681,10 +13714,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -13695,7 +13728,7 @@
         <v>74</v>
       </c>
       <c r="G122" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H122" t="s" s="2">
         <v>73</v>
@@ -13710,10 +13743,10 @@
         <v>114</v>
       </c>
       <c r="L122" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="M122" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="M122" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -13764,13 +13797,13 @@
         <v>73</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH122" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI122" t="s" s="2">
         <v>73</v>
@@ -13781,10 +13814,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -13795,7 +13828,7 @@
         <v>74</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H123" t="s" s="2">
         <v>73</v>
@@ -13807,13 +13840,13 @@
         <v>73</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>339</v>
+        <v>98</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -13864,27 +13897,27 @@
         <v>73</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI123" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -13895,7 +13928,7 @@
         <v>74</v>
       </c>
       <c r="G124" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H124" t="s" s="2">
         <v>73</v>
@@ -13907,13 +13940,13 @@
         <v>73</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>343</v>
+        <v>83</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>343</v>
+        <v>84</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -13964,38 +13997,38 @@
         <v>73</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>342</v>
+        <v>85</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH124" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI124" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G125" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H125" t="s" s="2">
         <v>73</v>
@@ -14007,15 +14040,17 @@
         <v>73</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="N125" s="2"/>
+        <v>90</v>
+      </c>
+      <c r="N125" t="s" s="2">
+        <v>91</v>
+      </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
         <v>73</v>
@@ -14052,43 +14087,43 @@
         <v>73</v>
       </c>
       <c r="AB125" t="s" s="2">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="AC125" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AD125" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE125" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH125" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI125" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
@@ -14101,24 +14136,26 @@
         <v>73</v>
       </c>
       <c r="I126" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J126" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="K126" t="s" s="2">
         <v>88</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="N126" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="O126" s="2"/>
+      <c r="O126" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="P126" t="s" s="2">
         <v>73</v>
       </c>
@@ -14154,19 +14191,19 @@
         <v>73</v>
       </c>
       <c r="AB126" t="s" s="2">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="AC126" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AD126" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE126" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>74</v>
@@ -14183,46 +14220,42 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G127" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H127" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I127" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="J127" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>88</v>
+        <v>343</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>105</v>
+        <v>344</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="O127" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>345</v>
+      </c>
+      <c r="N127" s="2"/>
+      <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
         <v>73</v>
       </c>
@@ -14270,27 +14303,27 @@
         <v>73</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>108</v>
+        <v>342</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH127" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI127" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -14301,7 +14334,7 @@
         <v>74</v>
       </c>
       <c r="G128" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H128" t="s" s="2">
         <v>73</v>
@@ -14316,10 +14349,10 @@
         <v>114</v>
       </c>
       <c r="L128" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="M128" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="M128" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -14370,13 +14403,13 @@
         <v>73</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH128" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI128" t="s" s="2">
         <v>73</v>
@@ -14387,10 +14420,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -14401,7 +14434,7 @@
         <v>74</v>
       </c>
       <c r="G129" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H129" t="s" s="2">
         <v>73</v>
@@ -14413,7 +14446,7 @@
         <v>73</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>114</v>
+        <v>350</v>
       </c>
       <c r="L129" t="s" s="2">
         <v>351</v>
@@ -14470,13 +14503,13 @@
         <v>73</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH129" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI129" t="s" s="2">
         <v>73</v>
@@ -14501,7 +14534,7 @@
         <v>74</v>
       </c>
       <c r="G130" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H130" t="s" s="2">
         <v>73</v>
@@ -14513,13 +14546,13 @@
         <v>73</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="L130" t="s" s="2">
         <v>354</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -14576,21 +14609,21 @@
         <v>74</v>
       </c>
       <c r="AH130" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI130" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -14613,13 +14646,13 @@
         <v>73</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>357</v>
+        <v>83</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>358</v>
+        <v>84</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
@@ -14670,7 +14703,7 @@
         <v>73</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>356</v>
+        <v>85</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>74</v>
@@ -14687,14 +14720,14 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
@@ -14713,15 +14746,17 @@
         <v>73</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>360</v>
+        <v>89</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="N132" s="2"/>
+        <v>90</v>
+      </c>
+      <c r="N132" t="s" s="2">
+        <v>91</v>
+      </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
         <v>73</v>
@@ -14758,19 +14793,19 @@
         <v>73</v>
       </c>
       <c r="AB132" t="s" s="2">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="AC132" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AD132" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE132" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>359</v>
+        <v>95</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>74</v>
@@ -14782,6 +14817,610 @@
         <v>73</v>
       </c>
       <c r="AJ132" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="B133" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="C133" s="2"/>
+      <c r="D133" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="E133" s="2"/>
+      <c r="F133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G133" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H133" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I133" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="J133" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="K133" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="L133" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M133" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="N133" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="O133" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="P133" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q133" s="2"/>
+      <c r="R133" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S133" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T133" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U133" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V133" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W133" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X133" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y133" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z133" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA133" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB133" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC133" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD133" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE133" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF133" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AG133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH133" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI133" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ133" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="C134" s="2"/>
+      <c r="D134" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E134" s="2"/>
+      <c r="F134" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G134" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H134" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I134" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J134" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K134" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L134" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M134" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="N134" s="2"/>
+      <c r="O134" s="2"/>
+      <c r="P134" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q134" s="2"/>
+      <c r="R134" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S134" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T134" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U134" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V134" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W134" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X134" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y134" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z134" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA134" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB134" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC134" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD134" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE134" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF134" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AG134" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH134" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI134" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ134" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="B135" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="C135" s="2"/>
+      <c r="D135" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E135" s="2"/>
+      <c r="F135" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G135" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H135" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I135" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J135" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K135" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L135" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M135" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="N135" s="2"/>
+      <c r="O135" s="2"/>
+      <c r="P135" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q135" s="2"/>
+      <c r="R135" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S135" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T135" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U135" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V135" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W135" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X135" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y135" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z135" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA135" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB135" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC135" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD135" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE135" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF135" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="AG135" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH135" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI135" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ135" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="B136" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="C136" s="2"/>
+      <c r="D136" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E136" s="2"/>
+      <c r="F136" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G136" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H136" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I136" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J136" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K136" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L136" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="M136" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="N136" s="2"/>
+      <c r="O136" s="2"/>
+      <c r="P136" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q136" s="2"/>
+      <c r="R136" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S136" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T136" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U136" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V136" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W136" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X136" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y136" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z136" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA136" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB136" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC136" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD136" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE136" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF136" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="AG136" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH136" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI136" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ136" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="B137" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="C137" s="2"/>
+      <c r="D137" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E137" s="2"/>
+      <c r="F137" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G137" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H137" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I137" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J137" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K137" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L137" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="M137" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="N137" s="2"/>
+      <c r="O137" s="2"/>
+      <c r="P137" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q137" s="2"/>
+      <c r="R137" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S137" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T137" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U137" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V137" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W137" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X137" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y137" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z137" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA137" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB137" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC137" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD137" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE137" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF137" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AG137" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH137" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI137" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ137" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="B138" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="C138" s="2"/>
+      <c r="D138" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E138" s="2"/>
+      <c r="F138" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G138" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H138" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I138" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J138" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K138" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L138" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="M138" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="N138" s="2"/>
+      <c r="O138" s="2"/>
+      <c r="P138" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q138" s="2"/>
+      <c r="R138" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S138" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T138" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U138" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V138" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W138" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X138" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y138" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z138" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA138" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB138" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC138" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD138" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE138" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF138" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AG138" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH138" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI138" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ138" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-lm-seltene.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-lm-seltene.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T15:16:54+00:00</t>
+    <t>2026-09-02T16:13:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -376,13 +376,13 @@
     <t>Untersuchungsanlass</t>
   </si>
   <si>
-    <t>Grund fuer den Besuch des SE-Patienten.</t>
+    <t>Grund für den Besuch des SE-Patienten.</t>
   </si>
   <si>
     <t>Seltene.anamneseUndDiagnostik.phaenotypisierung</t>
   </si>
   <si>
-    <t>Phaenotypisierung</t>
+    <t>Phänotypisierung</t>
   </si>
   <si>
     <t>Seltene.anamneseUndDiagnostik.phaenotypisierung.id</t>
@@ -400,7 +400,7 @@
     <t>HPO-Term des Symptoms</t>
   </si>
   <si>
-    <t>Phaenotypisierung des SE-Patienten mittels HPO-Term (Human Phenotype Ontology) oder anderer Terminologien (SNOMED CT, ICD-10, LOINC).</t>
+    <t>Phänotypisierung des SE-Patienten mittels HPO-Term (Human Phenotype Ontology) oder anderer Terminologien (SNOMED CT, ICD-10, LOINC).</t>
   </si>
   <si>
     <t>Seltene.anamneseUndDiagnostik.phaenotypisierung.hpoExcluded</t>
@@ -422,7 +422,7 @@
     <t>Status HPO-Term</t>
   </si>
   <si>
-    <t>Status oder Schweregrad des Phaenotyps (Present/Absent/Severity).</t>
+    <t>Status oder Schweregrad des Phänotyps (Present/Absent/Severity).</t>
   </si>
   <si>
     <t>Seltene.anamneseUndDiagnostik.phaenotypisierung.hpoVersion</t>
@@ -431,7 +431,7 @@
     <t>Version HPO-Term</t>
   </si>
   <si>
-    <t>Kennzeichnung der genutzten Version des ausgewaehlten HPO-Terms.</t>
+    <t>Kennzeichnung der genutzten Version des ausgewählten HPO-Terms.</t>
   </si>
   <si>
     <t>Seltene.anamneseUndDiagnostik.phaenotypisierung.zeitraumSymptom</t>
@@ -490,7 +490,7 @@
     <t>Verlauf Symptom</t>
   </si>
   <si>
-    <t>Aenderung des Verlaufs des Symptoms seit der vorherigen Untersuchung.</t>
+    <t>Änderung des Verlaufs des Symptoms seit der vorherigen Untersuchung.</t>
   </si>
   <si>
     <t>Seltene.anamneseUndDiagnostik.klinischeDiagnose</t>
@@ -583,7 +583,7 @@
     <t>Genetische Diagnose mit fehlender Penetranz</t>
   </si>
   <si>
-    <t>Gibt an, ob bei einer genetischen Diagnose die Penetranz (Wahrscheinlichkeit Genotyp bildet Phaenotyp aus) fehlt</t>
+    <t>Gibt an, ob bei einer genetischen Diagnose die Penetranz (Wahrscheinlichkeit Genotyp bildet Phänotyp aus) fehlt</t>
   </si>
   <si>
     <t>Seltene.anamneseUndDiagnostik.methodeDiagnosestellung</t>
@@ -800,7 +800,7 @@
     <t>Taillenumfang in cm</t>
   </si>
   <si>
-    <t>Taillenumfang des SE-Patienten in cm. Abzugrenzen vom Bauchumfang, der auf Nabelhoehe gemessen wird.</t>
+    <t>Taillenumfang des SE-Patienten in cm. Abzugrenzen vom Bauchumfang, der auf Nabelhöhe gemessen wird.</t>
   </si>
   <si>
     <t>Seltene.koerperlicheUntersuchung.taillenumfang.datumTaillenumfang</t>
@@ -857,7 +857,7 @@
     <t>Seltene.persoenlicheInfosIndexpatient</t>
   </si>
   <si>
-    <t>Persoenliche Informationen des Indexpatienten</t>
+    <t>Persönliche Informationen des Indexpatienten</t>
   </si>
   <si>
     <t>Seltene.persoenlicheInfosIndexpatient.id</t>
@@ -929,10 +929,10 @@
     <t>Seltene.familienanamnese.verwandtschaftsverhaeltnis</t>
   </si>
   <si>
-    <t>Verwandtschaftsverhaeltnis</t>
-  </si>
-  <si>
-    <t>Biologisches Verwandtschaftsverhaeltnis des Familienmitglieds zum Indexpatienten.</t>
+    <t>Verwandtschaftsverhältnis</t>
+  </si>
+  <si>
+    <t>Biologisches Verwandtschaftsverhältnis des Familienmitglieds zum Indexpatienten.</t>
   </si>
   <si>
     <t>Seltene.familienanamnese.geschlecht</t>
@@ -968,7 +968,7 @@
     <t>Penetranz</t>
   </si>
   <si>
-    <t>Gibt an, ob bei fehlender klinscher Penetranz (Wahrscheinlichkeit Genotyp bildet Phaenotyp aus) die genetische Diagnose vorliegt.</t>
+    <t>Gibt an, ob bei fehlender klinscher Penetranz (Wahrscheinlichkeit Genotyp bildet Phänotyp aus) die genetische Diagnose vorliegt.</t>
   </si>
   <si>
     <t>Seltene.familienanamnese.familienmitgliedVerstorben</t>
@@ -986,7 +986,7 @@
     <t>Tod durch seltene Erkrankung</t>
   </si>
   <si>
-    <t>Gibt an, ob die seltene Erkrankung zum Tod des Familienmitglieds beigetragen hat. Abzugrenzen von familienmitgliedVerstorben, das nur den Tod als solchen festhaelt.</t>
+    <t>Gibt an, ob die seltene Erkrankung zum Tod des Familienmitglieds beigetragen hat. Abzugrenzen von familienmitgliedVerstorben, das nur den Tod als solchen festhält.</t>
   </si>
   <si>
     <t>Seltene.familienanamnese.dokumentationsdatum</t>
@@ -1120,10 +1120,10 @@
     <t>Seltene.therapieForschung.therapie.durchgefuehrteTherapie</t>
   </si>
   <si>
-    <t>Durchgefuehrte Therapie</t>
-  </si>
-  <si>
-    <t>Tatsaechlich durchgeführte Therapie des SE-Patienten (mit oder ohne Studie mit heilender Intention).</t>
+    <t>Durchgeführte Therapie</t>
+  </si>
+  <si>
+    <t>Tatsächlich durchgeführte Therapie des SE-Patienten (mit oder ohne Studie mit heilender Intention).</t>
   </si>
   <si>
     <t>Seltene.therapieForschung.therapie.startdatumTherapie</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-lm-seltene.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-lm-seltene.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T16:13:05+00:00</t>
+    <t>2026-09-02T16:35:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-lm-seltene.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-lm-seltene.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T16:35:11+00:00</t>
+    <t>2026-09-02T16:52:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-lm-seltene.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-lm-seltene.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T16:52:58+00:00</t>
+    <t>2026-09-02T17:07:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-lm-seltene.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-lm-seltene.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:07:58+00:00</t>
+    <t>2026-09-02T17:34:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-lm-seltene.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-lm-seltene.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:34:23+00:00</t>
+    <t>2026-09-02T17:52:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-lm-seltene.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-lm-seltene.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:52:03+00:00</t>
+    <t>2026-09-02T18:22:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-lm-seltene.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-lm-seltene.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T18:22:51+00:00</t>
+    <t>2026-09-03T06:59:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-lm-seltene.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-lm-seltene.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T06:59:35+00:00</t>
+    <t>2026-09-03T07:17:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-lm-seltene.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-lm-seltene.xlsx
@@ -36,7 +36,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>MII_LM_SE</t>
+    <t>MII_LM_Seltene</t>
   </si>
   <si>
     <t>Title</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T07:17:59+00:00</t>
+    <t>2026-09-03T07:33:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-lm-seltene.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-lm-seltene.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T07:33:22+00:00</t>
+    <t>2026-09-03T09:08:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-lm-seltene.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-lm-seltene.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T09:08:22+00:00</t>
+    <t>2026-09-03T09:27:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-lm-seltene.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-lm-seltene.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T09:27:13+00:00</t>
+    <t>2026-09-03T09:44:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-lm-seltene.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-lm-seltene.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T09:44:41+00:00</t>
+    <t>2026-09-03T10:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
